--- a/港岛-寿臣山及浅水湾-深水湾径8号/深水湾径8号_销控明细表.xlsx
+++ b/港岛-寿臣山及浅水湾-深水湾径8号/深水湾径8号_销控明细表.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2018-11-13</t>
+          <t>2018-11-14</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2019-06-24</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2019-02-26</t>
+          <t>2019-02-27</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2019-05-15</t>
+          <t>2019-05-16</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2019-04-02</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2019-05-15</t>
+          <t>2019-05-16</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2021-05-02</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
+          <t>2018-11-16</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2021-08-22</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-11-27</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2019-02-26</t>
+          <t>2019-02-27</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2020-07-19</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2018-11-07</t>
+          <t>2018-11-08</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2020-11-15</t>
+          <t>2020-11-16</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4646,7 +4646,7 @@
           <t>B | 3641呎 (4+房)
 $39323万
 $108,000/呎
-(22年-01月-05日)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
           <t>B | 3641呎 (4+房)
 $24941万
 $68,500/呎
-(18年-11月-13日)</t>
+(18年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
           <t>B | 3641呎 (4+房)
 $25123万
 $69,000/呎
-(21年-03月-16日)</t>
+(21年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
           <t>B | 3641呎 (4+房)
 $24468万
 $67,200/呎
-(19年-06月-24日)</t>
+(19年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
           <t>A | 3407呎 (4+房)
 $21348万
 $62,660/呎
-(25年-06月-04日)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -4807,7 +4807,7 @@
           <t>B | 3641呎 (4+房)
 $22865万
 $62,800/呎
-(19年-02月-26日)</t>
+(19年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
           <t>B | 3641呎 (4+房)
 $22865万
 $62,800/呎
-(19年-05月-15日)</t>
+(19年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
           <t>B | 3641呎 (4+房)
 $22137万
 $60,800/呎
-(19年-04月-01日)</t>
+(19年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
           <t>B | 7568呎 (4+房)
 $60544万
 $80,000/呎
-(19年-05月-15日)</t>
+(19年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
           <t>C | 4214呎 (4+房)
 $45000万
 $106,787/呎
-(21年-10月-20日)</t>
+(21年-10月-21日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -5071,7 +5071,7 @@
           <t>C | 4214呎 (4+房)
 $37505万
 $89,000/呎
-(21年-05月-02日)</t>
+(21年-05月-03日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -5140,7 +5140,7 @@
           <t>C | 4214呎 (4+房)
 $31184万
 $74,000/呎
-(18年-11月-15日)</t>
+(18年-11月-16日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -5171,7 +5171,7 @@
           <t>D | 2865呎 (3房)
 $18622万
 $65,000/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
           <t>C | 4214呎 (4+房)
 $34555万
 $82,000/呎
-(21年-08月-22日)</t>
+(21年-08月-23日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -5194,7 +5194,7 @@
           <t>D | 2865呎 (3房)
 $17960万
 $62,688/呎
-(20年-09月-07日)</t>
+(20年-09月-08日)</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
           <t>C | 4214呎 (4+房)
 $29203万
 $69,300/呎
-(19年-02月-26日)</t>
+(19年-02月-27日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -5217,7 +5217,7 @@
           <t>D | 2865呎 (3房)
 $18050万
 $63,000/呎
-(20年-11月-26日)</t>
+(20年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
           <t>C | 4214呎 (4+房)
 $28770万
 $68,272/呎
-(18年-11月-07日)</t>
+(18年-11月-08日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -5240,7 +5240,7 @@
           <t>D | 2865呎 (3房)
 $17500万
 $61,082/呎
-(20年-07月-19日)</t>
+(20年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
           <t>D | 2865呎 (3房)
 $17476万
 $61,000/呎
-(20年-11月-15日)</t>
+(20年-11月-16日)</t>
         </is>
       </c>
     </row>

--- a/港岛-寿臣山及浅水湾-深水湾径8号/深水湾径8号_销控明细表.xlsx
+++ b/港岛-寿臣山及浅水湾-深水湾径8号/深水湾径8号_销控明细表.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4485,23 +4485,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>1座 销控网格图</t>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>深水湾径8号 - 独立屋销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -4532,357 +4532,83 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>18&amp;19</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>A | 6529呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>B | 7070呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1号屋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2号屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
+          <t>1号屋
+12566呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 3641呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$39323万
-$108,000/呎
-(22年-01月-06日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$24941万
-$68,500/呎
-(18年-11月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$25123万
-$69,000/呎
-(21年-03月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$24468万
-$67,200/呎
-(19年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-$21348万
-$62,660/呎
-(25年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$22865万
-$62,800/呎
-(19年-02月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$22865万
-$62,800/呎
-(19年-05月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$22137万
-$60,800/呎
-(19年-04月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>UG&amp;1&amp;2</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 7085呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>B | 7568呎 (4+房)
-$60544万
-$80,000/呎
-(19年-05月-16日)</t>
+          <t>2号屋
+7710呎 (3房)
+(待售)
+暂无价格
+暂无呎价</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4906,7 +4632,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>2座 销控网格图</t>
+          <t>1座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4686,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4970,7 +4696,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -4982,12 +4708,12 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4725,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>C | 7937呎 (4+房)
+          <t>A | 6529呎 (4+房)
 -
 -
 (待售)</t>
@@ -5007,7 +4733,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>D | 5785呎 (3房)
+          <t>B | 7070呎 (4+房)
 -
 -
 (待售)</t>
@@ -5022,7 +4748,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>C | 4214呎 (4+房)
+          <t>A | 3407呎 (4+房)
 -
 -
 (待售)</t>
@@ -5030,7 +4756,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>D | 2865呎 (3房)
+          <t>B | 3641呎 (4+房)
 -
 -
 (待售)</t>
@@ -5043,20 +4769,20 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$45000万
-$106,787/呎
-(21年-10月-21日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
 -
 -
 (待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$39323万
+$108,000/呎
+(22年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -5066,17 +4792,17 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$37505万
-$89,000/呎
-(21年-05月-03日)</t>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>D | 2865呎 (3房)
+          <t>B | 3641呎 (4+房)
 -
 -
 (待售)</t>
@@ -5091,7 +4817,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>C | 4214呎 (4+房)
+          <t>A | 3407呎 (4+房)
 -
 -
 (待售)</t>
@@ -5099,7 +4825,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>D | 2865呎 (3房)
+          <t>B | 3641呎 (4+房)
 -
 -
 (待售)</t>
@@ -5114,7 +4840,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>C | 4214呎 (4+房)
+          <t>A | 3407呎 (4+房)
 -
 -
 (待售)</t>
@@ -5122,7 +4848,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>D | 2865呎 (3房)
+          <t>B | 3641呎 (4+房)
 -
 -
 (待售)</t>
@@ -5135,20 +4861,20 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$31184万
-$74,000/呎
-(18年-11月-16日)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
 -
 -
 (待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$24941万
+$68,500/呎
+(18年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -5160,7 +4886,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>C | 4214呎 (4+房)
+          <t>A | 3407呎 (4+房)
 -
 -
 (待售)</t>
@@ -5168,10 +4894,10 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>D | 2865呎 (3房)
-$18622万
-$65,000/呎
-(21年-02月-05日)</t>
+          <t>B | 3641呎 (4+房)
+$25123万
+$69,000/呎
+(21年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -5181,20 +4907,20 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$34555万
-$82,000/呎
-(21年-08月-23日)</t>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>D | 2865呎 (3房)
-$17960万
-$62,688/呎
-(20年-09月-08日)</t>
+          <t>B | 3641呎 (4+房)
+$24468万
+$67,200/呎
+(19年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -5206,18 +4932,18 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>C | 4214呎 (4+房)
-$29203万
-$69,300/呎
+          <t>A | 3407呎 (4+房)
+$21348万
+$62,660/呎
+(25年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$22865万
+$62,800/呎
 (19年-02月-27日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-$18050万
-$63,000/呎
-(20年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -5227,20 +4953,20 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$28770万
-$68,272/呎
-(18年-11月-08日)</t>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>D | 2865呎 (3房)
-$17500万
-$61,082/呎
-(20年-07月-20日)</t>
+          <t>B | 3641呎 (4+房)
+$22865万
+$62,800/呎
+(19年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -5252,7 +4978,7 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>C | 4214呎 (4+房)
+          <t>A | 3407呎 (4+房)
 -
 -
 (待售)</t>
@@ -5260,10 +4986,10 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>D | 2865呎 (3房)
-$17476万
-$61,000/呎
-(20年-11月-16日)</t>
+          <t>B | 3641呎 (4+房)
+$22137万
+$60,800/呎
+(19年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -5275,18 +5001,18 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>C | 8475呎 (4+房)
+          <t>A | 7085呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>D | 6322呎 (4+房)
--
--
-(待售)</t>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 7568呎 (4+房)
+$60544万
+$80,000/呎
+(19年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -5305,23 +5031,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>深水湾径8号 - 独立屋销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -5352,83 +5078,357 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="25" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="26" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>类型/位置</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1号屋</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2号屋</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>独立屋</t>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>18&amp;19</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>C | 7937呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>D | 5785呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>1号屋
-12566呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
+          <t>C | 4214呎 (4+房)
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>2号屋
-7710呎 (3房)
-(待售)
-暂无价格
-暂无呎价</t>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$45000万
+$106,787/呎
+(21年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$37505万
+$89,000/呎
+(21年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$31184万
+$74,000/呎
+(18年-11月-16日)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+$18622万
+$65,000/呎
+(21年-02月-05日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$34555万
+$82,000/呎
+(21年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+$17960万
+$62,688/呎
+(20年-09月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$29203万
+$69,300/呎
+(19年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+$18050万
+$63,000/呎
+(20年-11月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$28770万
+$68,272/呎
+(18年-11月-08日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+$17500万
+$61,082/呎
+(20年-07月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+$17476万
+$61,000/呎
+(20年-11月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>UG&amp;1&amp;2</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>C | 8475呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>D | 6322呎 (4+房)
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/港岛-寿臣山及浅水湾-深水湾径8号/深水湾径8号_销控明细表.xlsx
+++ b/港岛-寿臣山及浅水湾-深水湾径8号/深水湾径8号_销控明细表.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4485,23 +4485,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>深水湾径8号 - 独立屋销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -4532,83 +4532,357 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="25" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="26" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>类型/位置</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1号屋</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2号屋</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>独立屋</t>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>18&amp;19</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 6529呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 7070呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>1号屋
-12566呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>2号屋
-7710呎 (3房)
-(待售)
-暂无价格
-暂无呎价</t>
+          <t>B | 3641呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$39323万
+$108,000/呎
+(22年-01月-06日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$24941万
+$68,500/呎
+(18年-11月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$25123万
+$69,000/呎
+(21年-03月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$24468万
+$67,200/呎
+(19年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+$21348万
+$62,660/呎
+(25年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$22865万
+$62,800/呎
+(19年-02月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$22865万
+$62,800/呎
+(19年-05月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$22137万
+$60,800/呎
+(19年-04月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>UG&amp;1&amp;2</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 7085呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 7568呎 (4+房)
+$60544万
+$80,000/呎
+(19年-05月-16日)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4632,7 +4906,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>1座 销控网格图</t>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4960,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4696,7 +4970,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4982,12 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4999,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 6529呎 (4+房)
+          <t>C | 7937呎 (4+房)
 -
 -
 (待售)</t>
@@ -4733,7 +5007,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 7070呎 (4+房)
+          <t>D | 5785呎 (3房)
 -
 -
 (待售)</t>
@@ -4748,7 +5022,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 3407呎 (4+房)
+          <t>C | 4214呎 (4+房)
 -
 -
 (待售)</t>
@@ -4756,7 +5030,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 3641呎 (4+房)
+          <t>D | 2865呎 (3房)
 -
 -
 (待售)</t>
@@ -4769,20 +5043,20 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$45000万
+$106,787/呎
+(21年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
 -
 -
 (待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$39323万
-$108,000/呎
-(22年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -4792,17 +5066,17 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$37505万
+$89,000/呎
+(21年-05月-03日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 3641呎 (4+房)
+          <t>D | 2865呎 (3房)
 -
 -
 (待售)</t>
@@ -4817,7 +5091,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 3407呎 (4+房)
+          <t>C | 4214呎 (4+房)
 -
 -
 (待售)</t>
@@ -4825,7 +5099,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 3641呎 (4+房)
+          <t>D | 2865呎 (3房)
 -
 -
 (待售)</t>
@@ -4840,7 +5114,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 3407呎 (4+房)
+          <t>C | 4214呎 (4+房)
 -
 -
 (待售)</t>
@@ -4848,7 +5122,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 3641呎 (4+房)
+          <t>D | 2865呎 (3房)
 -
 -
 (待售)</t>
@@ -4861,20 +5135,20 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$31184万
+$74,000/呎
+(18年-11月-16日)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
 -
 -
 (待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$24941万
-$68,500/呎
-(18年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -4886,7 +5160,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 3407呎 (4+房)
+          <t>C | 4214呎 (4+房)
 -
 -
 (待售)</t>
@@ -4894,10 +5168,10 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>B | 3641呎 (4+房)
-$25123万
-$69,000/呎
-(21年-03月-17日)</t>
+          <t>D | 2865呎 (3房)
+$18622万
+$65,000/呎
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -4907,20 +5181,20 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$34555万
+$82,000/呎
+(21年-08月-23日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 3641呎 (4+房)
-$24468万
-$67,200/呎
-(19年-06月-25日)</t>
+          <t>D | 2865呎 (3房)
+$17960万
+$62,688/呎
+(20年-09月-08日)</t>
         </is>
       </c>
     </row>
@@ -4932,18 +5206,18 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 3407呎 (4+房)
-$21348万
-$62,660/呎
-(25年-06月-05日)</t>
+          <t>C | 4214呎 (4+房)
+$29203万
+$69,300/呎
+(19年-02月-27日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>B | 3641呎 (4+房)
-$22865万
-$62,800/呎
-(19年-02月-27日)</t>
+          <t>D | 2865呎 (3房)
+$18050万
+$63,000/呎
+(20年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -4953,20 +5227,20 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
--
--
-(待售)</t>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$28770万
+$68,272/呎
+(18年-11月-08日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>B | 3641呎 (4+房)
-$22865万
-$62,800/呎
-(19年-05月-16日)</t>
+          <t>D | 2865呎 (3房)
+$17500万
+$61,082/呎
+(20年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -4978,7 +5252,7 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 3407呎 (4+房)
+          <t>C | 4214呎 (4+房)
 -
 -
 (待售)</t>
@@ -4986,10 +5260,10 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>B | 3641呎 (4+房)
-$22137万
-$60,800/呎
-(19年-04月-02日)</t>
+          <t>D | 2865呎 (3房)
+$17476万
+$61,000/呎
+(20年-11月-16日)</t>
         </is>
       </c>
     </row>
@@ -5001,18 +5275,18 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 7085呎 (4+房)
+          <t>C | 8475呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>B | 7568呎 (4+房)
-$60544万
-$80,000/呎
-(19年-05月-16日)</t>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>D | 6322呎 (4+房)
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -5031,23 +5305,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>2座 销控网格图</t>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>深水湾径8号 - 独立屋销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -5078,357 +5352,83 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>18&amp;19</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>C | 7937呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>D | 5785呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1号屋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2号屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>C | 4214呎 (4+房)
--
--
-(待售)</t>
+          <t>1号屋
+12566呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>D | 2865呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$45000万
-$106,787/呎
-(21年-10月-21日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$37505万
-$89,000/呎
-(21年-05月-03日)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$31184万
-$74,000/呎
-(18年-11月-16日)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-$18622万
-$65,000/呎
-(21年-02月-05日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$34555万
-$82,000/呎
-(21年-08月-23日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-$17960万
-$62,688/呎
-(20年-09月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$29203万
-$69,300/呎
-(19年-02月-27日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-$18050万
-$63,000/呎
-(20年-11月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$28770万
-$68,272/呎
-(18年-11月-08日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-$17500万
-$61,082/呎
-(20年-07月-20日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-$17476万
-$61,000/呎
-(20年-11月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>UG&amp;1&amp;2</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>C | 8475呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>D | 6322呎 (4+房)
--
--
-(待售)</t>
+          <t>2号屋
+7710呎 (3房)
+(待售)
+暂无价格
+暂无呎价</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
